--- a/workflow/2_Miscellaneous/OSeMOSYS_Structure.xlsx
+++ b/workflow/2_Miscellaneous/OSeMOSYS_Structure.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78393ED2-8464-4FB0-88F2-9CC445FB8923}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F5D5D7-4BE1-4FD1-9653-CBF78B3D4A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="164">
   <si>
     <t>number</t>
   </si>
@@ -853,76 +853,76 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8A1DB5-AB21-4E2D-94E4-FE18AAF65A94}">
   <dimension ref="A1:BQ8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" customWidth="1"/>
-    <col min="5" max="5" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.33203125" customWidth="1"/>
-    <col min="12" max="12" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="21.44140625" customWidth="1"/>
-    <col min="17" max="17" width="28.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+    <col min="5" max="5" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.28515625" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="26.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.42578125" customWidth="1"/>
+    <col min="17" max="17" width="28.7109375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="15" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="18.88671875" customWidth="1"/>
-    <col min="27" max="27" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.33203125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="22.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="18.85546875" customWidth="1"/>
+    <col min="27" max="27" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="9.7109375" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="18" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="23.33203125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="23" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="33.88671875" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="33.44140625" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="39.44140625" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="44.88671875" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="33.42578125" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="39.42578125" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="28" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="19.85546875" bestFit="1" customWidth="1"/>
     <col min="43" max="43" width="10" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="30.6640625" customWidth="1"/>
-    <col min="52" max="52" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="20.33203125" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="30.7109375" customWidth="1"/>
+    <col min="52" max="52" width="22.85546875" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="20.28515625" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="55" max="55" width="22" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="58" max="58" width="22" bestFit="1" customWidth="1"/>
     <col min="59" max="59" width="18" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="23.140625" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="38" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="38.6640625" bestFit="1" customWidth="1"/>
-    <col min="63" max="64" width="38.6640625" customWidth="1"/>
+    <col min="62" max="62" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="63" max="64" width="38.7109375" customWidth="1"/>
     <col min="65" max="65" width="12" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="24" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="7.5546875" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -960,7 +960,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1169,7 +1169,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="D3">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <f t="shared" si="0"/>
@@ -1250,203 +1250,203 @@
         <v>2</v>
       </c>
       <c r="U3">
-        <f>+COUNTA(U4:U1048576)</f>
+        <f t="shared" ref="U3:AF3" si="2">+COUNTA(U4:U1048576)</f>
         <v>3</v>
       </c>
       <c r="V3">
-        <f>+COUNTA(V4:V1048576)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="W3">
-        <f>+COUNTA(W4:W1048576)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="X3">
-        <f>+COUNTA(X4:X1048576)</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="Y3">
-        <f>+COUNTA(Y4:Y1048576)</f>
+        <f t="shared" si="2"/>
         <v>5</v>
       </c>
       <c r="Z3">
-        <f>+COUNTA(Z4:Z1048576)</f>
-        <v>2</v>
-      </c>
-      <c r="AA3">
-        <f>+COUNTA(AA4:AA1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AB3">
-        <f>+COUNTA(AB4:AB1048576)</f>
-        <v>4</v>
-      </c>
-      <c r="AC3">
-        <f>+COUNTA(AC4:AC1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AD3">
-        <f>+COUNTA(AD4:AD1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AE3">
-        <f>+COUNTA(AE4:AE1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AF3">
-        <f>+COUNTA(AF4:AF1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AG3">
-        <f t="shared" ref="AG3:AS3" si="2">+COUNTA(AG4:AG1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AH3">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="AI3">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="AJ3">
-        <f t="shared" si="2"/>
-        <v>3</v>
-      </c>
-      <c r="AK3">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="AL3">
+      <c r="AA3">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="AM3">
+        <v>3</v>
+      </c>
+      <c r="AB3">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="AN3">
+        <v>4</v>
+      </c>
+      <c r="AC3">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AO3">
+      <c r="AD3">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AP3">
+      <c r="AE3">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AQ3">
+      <c r="AF3">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="AR3">
-        <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="AS3">
-        <f t="shared" si="2"/>
-        <v>5</v>
-      </c>
-      <c r="AT3">
-        <f>+COUNTA(AT4:AT1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AU3">
-        <f>+COUNTA(AU4:AU1048576)</f>
-        <v>2</v>
-      </c>
-      <c r="AV3">
-        <f>+COUNTA(AV4:AV1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AW3">
-        <f>+COUNTA(AW4:AW1048576)</f>
-        <v>3</v>
-      </c>
-      <c r="AX3">
-        <f>+COUNTA(AX4:AX1048576)</f>
-        <v>2</v>
-      </c>
-      <c r="AY3">
-        <f>+COUNTA(AY4:AY1048576)</f>
-        <v>5</v>
-      </c>
-      <c r="AZ3">
-        <f t="shared" ref="AZ3:BQ3" si="3">+COUNTA(AZ4:AZ7)</f>
-        <v>4</v>
-      </c>
-      <c r="BA3">
+      <c r="AG3">
+        <f t="shared" ref="AG3:AS3" si="3">+COUNTA(AG4:AG1048576)</f>
+        <v>3</v>
+      </c>
+      <c r="AH3">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="BB3">
+        <v>3</v>
+      </c>
+      <c r="AI3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AJ3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AK3">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="BC3">
+      <c r="AL3">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="BD3">
+      <c r="AM3">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="BE3">
+      <c r="AN3">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="BF3">
+      <c r="AO3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AP3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AQ3">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="AR3">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
+      <c r="AS3">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="AT3">
+        <f t="shared" ref="AT3:AY3" si="4">+COUNTA(AT4:AT1048576)</f>
+        <v>3</v>
+      </c>
+      <c r="AU3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AV3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AW3">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="AX3">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="AY3">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="AZ3">
+        <f t="shared" ref="AZ3:BQ3" si="5">+COUNTA(AZ4:AZ7)</f>
+        <v>4</v>
+      </c>
+      <c r="BA3">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="BB3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="BC3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="BD3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="BE3">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="BF3">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
       <c r="BG3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="BH3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="BI3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BJ3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BK3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BL3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BM3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="BN3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BO3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BP3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>4</v>
       </c>
       <c r="BQ3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1652,7 +1652,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:69" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1852,7 +1852,10 @@
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:69" x14ac:dyDescent="0.25">
+      <c r="D6" t="s">
+        <v>8</v>
+      </c>
       <c r="E6" t="s">
         <v>12</v>
       </c>
@@ -1989,7 +1992,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>8</v>
       </c>
@@ -2048,7 +2051,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:69" x14ac:dyDescent="0.25">
       <c r="V8" t="s">
         <v>8</v>
       </c>
@@ -2071,76 +2074,76 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A61DBA02-50DA-45DC-88DC-E3B8D7B75762}">
   <dimension ref="A1:BN9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.88671875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="30" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="17" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="30.6640625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="23.109375" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.5703125" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="24.140625" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="28" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="25.33203125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="32.33203125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="28.44140625" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="25.28515625" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="32.28515625" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28.42578125" bestFit="1" customWidth="1"/>
     <col min="38" max="38" width="30" bestFit="1" customWidth="1"/>
     <col min="39" max="39" width="24" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="36" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="33.33203125" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="37.44140625" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="21.6640625" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="31.5546875" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="24.44140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="34.88671875" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="30.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="33.28515625" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="31.5703125" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="34.85546875" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="30.28515625" bestFit="1" customWidth="1"/>
     <col min="52" max="52" width="20" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="20.5546875" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="19.5546875" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="19.88671875" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="25.88671875" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="24.5546875" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="23.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="23.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="20.7109375" bestFit="1" customWidth="1"/>
     <col min="61" max="61" width="22" bestFit="1" customWidth="1"/>
-    <col min="62" max="63" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="24.6640625" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="62" max="63" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="24.7109375" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="27.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -2166,7 +2169,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -2366,7 +2369,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -2631,7 +2634,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:66" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>7</v>
       </c>
@@ -2828,7 +2831,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:66" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>11</v>
       </c>
@@ -3025,7 +3028,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:66" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
         <v>12</v>
       </c>
@@ -3204,7 +3207,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:66" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
         <v>8</v>
       </c>
@@ -3290,7 +3293,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:66" x14ac:dyDescent="0.25">
       <c r="J8" t="s">
         <v>8</v>
       </c>
@@ -3337,7 +3340,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:66" x14ac:dyDescent="0.25">
       <c r="O9" t="s">
         <v>8</v>
       </c>

--- a/workflow/2_Miscellaneous/OSeMOSYS_Structure.xlsx
+++ b/workflow/2_Miscellaneous/OSeMOSYS_Structure.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F5D5D7-4BE1-4FD1-9653-CBF78B3D4A67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D75ABCD1-BEBB-4D42-969E-3250EA7CEC74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="parameters" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="165">
   <si>
     <t>number</t>
   </si>
@@ -521,6 +521,9 @@
   </si>
   <si>
     <t>TechnologyActivityByModeUpperLimit</t>
+  </si>
+  <si>
+    <t>UDCMultiplierDemand</t>
   </si>
 </sst>
 </file>
@@ -852,7 +855,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D8A1DB5-AB21-4E2D-94E4-FE18AAF65A94}">
-  <dimension ref="A1:BQ8"/>
+  <dimension ref="A1:BR8"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
@@ -919,10 +922,11 @@
     <col min="66" max="66" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="67" max="67" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="68" max="68" width="24" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="24" customWidth="1"/>
+    <col min="70" max="70" width="7.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -960,7 +964,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1166,10 +1170,13 @@
         <v>160</v>
       </c>
       <c r="BQ2" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="BR2" s="2" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="3" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:70" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -1374,7 +1381,7 @@
         <v>5</v>
       </c>
       <c r="AZ3">
-        <f t="shared" ref="AZ3:BQ3" si="5">+COUNTA(AZ4:AZ7)</f>
+        <f t="shared" ref="AZ3:BR3" si="5">+COUNTA(AZ4:AZ7)</f>
         <v>4</v>
       </c>
       <c r="BA3">
@@ -1442,11 +1449,14 @@
         <v>4</v>
       </c>
       <c r="BQ3">
+        <v>4</v>
+      </c>
+      <c r="BR3">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
@@ -1651,8 +1661,11 @@
       <c r="BQ4" t="s">
         <v>7</v>
       </c>
+      <c r="BR4" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="5" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:70" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>8</v>
       </c>
@@ -1849,10 +1862,13 @@
         <v>10</v>
       </c>
       <c r="BQ5" t="s">
+        <v>12</v>
+      </c>
+      <c r="BR5" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="6" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:70" x14ac:dyDescent="0.25">
       <c r="D6" t="s">
         <v>8</v>
       </c>
@@ -1991,8 +2007,11 @@
       <c r="BP6" t="s">
         <v>161</v>
       </c>
+      <c r="BQ6" t="s">
+        <v>161</v>
+      </c>
     </row>
-    <row r="7" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:70" x14ac:dyDescent="0.25">
       <c r="E7" t="s">
         <v>8</v>
       </c>
@@ -2050,8 +2069,11 @@
       <c r="BP7" t="s">
         <v>8</v>
       </c>
+      <c r="BQ7" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="8" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:70" x14ac:dyDescent="0.25">
       <c r="V8" t="s">
         <v>8</v>
       </c>
@@ -3363,6 +3385,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100BAD73B84EC2FBA4AB6031CFB79C3D0E0" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1d8e6320e34b5f71545ca20c1fb39b21">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c4f98862-adfd-4d9c-a945-852f80f0eb51" xmlns:ns3="b9355cc9-2d41-4aa9-bfbc-bd016a1e1a01" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3f42cd320e09c56919cd7e955403e252" ns2:_="" ns3:_="">
     <xsd:import namespace="c4f98862-adfd-4d9c-a945-852f80f0eb51"/>
@@ -3579,16 +3610,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B01A19C5-D28B-42D4-9982-2E783BA97AE3}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C1290C1A-1675-4114-9589-C954F945D8B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3605,12 +3635,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B01A19C5-D28B-42D4-9982-2E783BA97AE3}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>